--- a/data/ecc_supply_to_mcc_with_losses.xlsx
+++ b/data/ecc_supply_to_mcc_with_losses.xlsx
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="BJ13" s="8">
-        <v>5820.73286270895</v>
+        <v>5820.73286270896</v>
       </c>
       <c r="BK13" s="8">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="BN13" s="8">
-        <v>67354.0211167643</v>
+        <v>67354.0211167639</v>
       </c>
       <c r="BO13" s="8">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="BX13" s="8">
-        <v>3155.64534081532</v>
+        <v>3155.64534081533</v>
       </c>
       <c r="BY13" s="8">
         <v>0</v>
@@ -6008,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="8">
-        <v>54768.7189038245</v>
+        <v>54768.7189038251</v>
       </c>
       <c r="BJ42" s="8">
         <v>0</v>
@@ -6070,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="CE42" s="8">
-        <v>0.72465121788954</v>
+        <v>0.724651217889545</v>
       </c>
       <c r="CF42" s="8">
         <v>0</v>
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="BX49" s="8">
-        <v>4140.47436592439</v>
+        <v>4140.47436592437</v>
       </c>
       <c r="BY49" s="8">
         <v>0</v>
@@ -8093,7 +8093,7 @@
         <v>0</v>
       </c>
       <c r="BJ61" s="8">
-        <v>42469.4304457101</v>
+        <v>42469.4304457103</v>
       </c>
       <c r="BK61" s="8">
         <v>0</v>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="BG65" s="8">
-        <v>-0.000000000428676675892715</v>
+        <v>-0.000000000000338745348570462</v>
       </c>
       <c r="BH65" s="8">
         <v>0</v>
@@ -8480,7 +8480,7 @@
         <v>0</v>
       </c>
       <c r="BK67" s="8">
-        <v>-0.000000000612396959908876</v>
+        <v>-0.000000000000483923276711564</v>
       </c>
       <c r="BL67" s="8">
         <v>0</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="BJ68" s="8">
-        <v>62501.1156779948</v>
+        <v>62501.1156779955</v>
       </c>
       <c r="BK68" s="8">
         <v>0</v>
@@ -8708,7 +8708,7 @@
         <v>0</v>
       </c>
       <c r="BW70" s="8">
-        <v>273.730001811498</v>
+        <v>273.730001811503</v>
       </c>
       <c r="BX70" s="8">
         <v>0</v>
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="BN74" s="8">
-        <v>2369.24361812092</v>
+        <v>2369.24361812096</v>
       </c>
       <c r="BO74" s="8">
         <v>0</v>
@@ -9641,7 +9641,7 @@
         <v>0</v>
       </c>
       <c r="BN85" s="8">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="BO85" s="8">
         <v>0</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="BO86" s="8">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="BP86" s="8">
         <v>0</v>
@@ -10214,7 +10214,7 @@
         <v>0</v>
       </c>
       <c r="BM94" s="8">
-        <v>10007.2898093627</v>
+        <v>10007.2898093626</v>
       </c>
       <c r="BN94" s="8">
         <v>0</v>
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="BU95" s="8">
-        <v>3605152.2885694</v>
+        <v>3605152.28856941</v>
       </c>
       <c r="BV95" s="8">
         <v>0</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="BX96" s="8">
-        <v>643.118931908688</v>
+        <v>643.118931908693</v>
       </c>
       <c r="BY96" s="8">
         <v>0</v>
@@ -10436,7 +10436,7 @@
         <v>0</v>
       </c>
       <c r="BW97" s="8">
-        <v>643.118931908688</v>
+        <v>643.118931908693</v>
       </c>
       <c r="BX97" s="8">
         <v>0</v>
@@ -10497,7 +10497,7 @@
         <v>0</v>
       </c>
       <c r="BV98" s="8">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="BW98" s="8">
         <v>0</v>
@@ -10543,7 +10543,7 @@
         <v>0</v>
       </c>
       <c r="BP99" s="8">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="BQ99" s="8">
         <v>0</v>
@@ -10586,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="8">
-        <v>20810.701307918</v>
+        <v>20810.7013079177</v>
       </c>
       <c r="BJ100" s="8">
         <v>0</v>
@@ -10595,13 +10595,13 @@
         <v>0</v>
       </c>
       <c r="BL100" s="8">
-        <v>0.0000000000917665618625633</v>
+        <v>-0.000000000213697384684882</v>
       </c>
       <c r="BM100" s="8">
         <v>0</v>
       </c>
       <c r="BN100" s="8">
-        <v>3023109.57430776</v>
+        <v>3023109.57430779</v>
       </c>
       <c r="BO100" s="8">
         <v>0</v>
@@ -10653,7 +10653,7 @@
         <v>0</v>
       </c>
       <c r="BJ101" s="8">
-        <v>2915788.43397589</v>
+        <v>2915788.43397592</v>
       </c>
       <c r="BK101" s="8">
         <v>0</v>
@@ -10762,7 +10762,7 @@
         <v>0</v>
       </c>
       <c r="BY102" s="8">
-        <v>20456.4061899525</v>
+        <v>20456.406189953</v>
       </c>
     </row>
     <row r="103">
@@ -10903,7 +10903,7 @@
         <v>0</v>
       </c>
       <c r="BH105" s="8">
-        <v>0.000000000000914962744368463</v>
+        <v>0.0000000000000135419641776167</v>
       </c>
       <c r="BI105" s="8">
         <v>0</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="BN105" s="8">
-        <v>4390.22190228729</v>
+        <v>4390.22190228727</v>
       </c>
       <c r="BO105" s="8">
         <v>0</v>
@@ -10994,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="BQ106" s="8">
-        <v>4368.51223387172</v>
+        <v>4368.51223387163</v>
       </c>
       <c r="BR106" s="8">
         <v>0</v>
@@ -11113,7 +11113,7 @@
         <v>0</v>
       </c>
       <c r="BN108" s="8">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="BO108" s="8">
         <v>0</v>
@@ -11189,7 +11189,7 @@
         <v>0</v>
       </c>
       <c r="BR109" s="8">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="BS109" s="8">
         <v>0</v>
@@ -11369,7 +11369,7 @@
         <v>0</v>
       </c>
       <c r="BN112" s="8">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="BO112" s="8">
         <v>0</v>
@@ -11451,7 +11451,7 @@
         <v>0</v>
       </c>
       <c r="BT113" s="8">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="BU113" s="8">
         <v>0</v>
@@ -11674,7 +11674,7 @@
         <v>0</v>
       </c>
       <c r="BJ119" s="7">
-        <v>42469.4304457101</v>
+        <v>42469.4304457103</v>
       </c>
       <c r="BK119" s="7">
         <v>0</v>
@@ -11965,7 +11965,7 @@
         </is>
       </c>
       <c r="BG123" s="7">
-        <v>-0.000000000428676675892715</v>
+        <v>-0.000000000000338745348570462</v>
       </c>
       <c r="BH123" s="7">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="BK125" s="7">
-        <v>-0.000000000612396959908876</v>
+        <v>-0.000000000000483923276711564</v>
       </c>
       <c r="BL125" s="7">
         <v>0</v>
@@ -12199,7 +12199,7 @@
         <v>0</v>
       </c>
       <c r="BJ126" s="7">
-        <v>62501.1156779948</v>
+        <v>62501.1156779955</v>
       </c>
       <c r="BK126" s="7">
         <v>0</v>
@@ -12388,7 +12388,7 @@
         <v>0</v>
       </c>
       <c r="BW128" s="7">
-        <v>273.730001811498</v>
+        <v>273.730001811503</v>
       </c>
       <c r="BX128" s="7">
         <v>0</v>
@@ -12424,7 +12424,7 @@
         <v>0</v>
       </c>
       <c r="BJ129" s="7">
-        <v>5820.73286270895</v>
+        <v>5820.73286270896</v>
       </c>
       <c r="BK129" s="7">
         <v>0</v>
@@ -12436,7 +12436,7 @@
         <v>0</v>
       </c>
       <c r="BN129" s="7">
-        <v>67354.0211167643</v>
+        <v>67354.0211167639</v>
       </c>
       <c r="BO129" s="7">
         <v>0</v>
@@ -12466,7 +12466,7 @@
         <v>0</v>
       </c>
       <c r="BX129" s="7">
-        <v>3155.64534081532</v>
+        <v>3155.64534081533</v>
       </c>
       <c r="BY129" s="7">
         <v>0</v>
@@ -12661,7 +12661,7 @@
         <v>0</v>
       </c>
       <c r="BN132" s="7">
-        <v>2369.24361812092</v>
+        <v>2369.24361812096</v>
       </c>
       <c r="BO132" s="7">
         <v>0</v>
@@ -12780,7 +12780,7 @@
         <v>0</v>
       </c>
       <c r="CD133" s="2">
-        <v>-0.000000000257206209762651</v>
+        <v>-0.000000000000203247370524871</v>
       </c>
     </row>
     <row r="134">
@@ -12930,7 +12930,7 @@
         <v>0</v>
       </c>
       <c r="CD135" s="2">
-        <v>4673.82474422194</v>
+        <v>4673.82474422187</v>
       </c>
     </row>
     <row r="136">
@@ -13080,7 +13080,7 @@
         <v>0</v>
       </c>
       <c r="CD137" s="2">
-        <v>-0.000000000183720345295316</v>
+        <v>-0.00000000000014517797656461</v>
       </c>
     </row>
     <row r="138">
@@ -13230,7 +13230,7 @@
         <v>0</v>
       </c>
       <c r="CD139" s="2">
-        <v>13371.4084106379</v>
+        <v>13371.4084106407</v>
       </c>
     </row>
     <row r="140">
@@ -13305,7 +13305,7 @@
         <v>0</v>
       </c>
       <c r="CD140" s="2">
-        <v>60456.4790869308</v>
+        <v>60456.4790869312</v>
       </c>
     </row>
     <row r="141">
@@ -13380,7 +13380,7 @@
         <v>0</v>
       </c>
       <c r="CD141" s="2">
-        <v>0.000000000000777718806752768</v>
+        <v>0.000000000000011510676567027</v>
       </c>
     </row>
     <row r="142">
@@ -13486,7 +13486,7 @@
         <v>0</v>
       </c>
       <c r="BN143" s="7">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="BO143" s="7">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>0</v>
       </c>
       <c r="BO144" s="7">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="BP144" s="7">
         <v>0</v>
@@ -13830,7 +13830,7 @@
         <v>0</v>
       </c>
       <c r="CD147" s="2">
-        <v>122301.52398651</v>
+        <v>122301.523986508</v>
       </c>
     </row>
     <row r="148">
@@ -14130,7 +14130,7 @@
         <v>0</v>
       </c>
       <c r="CD151" s="2">
-        <v>2069180.95381487</v>
+        <v>2069180.9538149</v>
       </c>
     </row>
     <row r="152">
@@ -14158,7 +14158,7 @@
         <v>0</v>
       </c>
       <c r="BM152" s="7">
-        <v>10007.2898093627</v>
+        <v>10007.2898093626</v>
       </c>
       <c r="BN152" s="7">
         <v>0</v>
@@ -14257,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="BU153" s="7">
-        <v>3605152.2885694</v>
+        <v>3605152.28856941</v>
       </c>
       <c r="BV153" s="7">
         <v>0</v>
@@ -14341,7 +14341,7 @@
         <v>0</v>
       </c>
       <c r="BX154" s="7">
-        <v>643.118931908688</v>
+        <v>643.118931908693</v>
       </c>
       <c r="BY154" s="7">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="BW155" s="7">
-        <v>643.118931908688</v>
+        <v>643.118931908693</v>
       </c>
       <c r="BX155" s="7">
         <v>0</v>
@@ -14485,7 +14485,7 @@
         <v>0</v>
       </c>
       <c r="BV156" s="7">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="BW156" s="7">
         <v>0</v>
@@ -14542,7 +14542,7 @@
         <v>0</v>
       </c>
       <c r="BP157" s="7">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="BQ157" s="7">
         <v>0</v>
@@ -14596,7 +14596,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="7">
-        <v>75579.4202117425</v>
+        <v>75579.4202117428</v>
       </c>
       <c r="BJ158" s="7">
         <v>0</v>
@@ -14605,13 +14605,13 @@
         <v>0</v>
       </c>
       <c r="BL158" s="7">
-        <v>0.0000000000917665618625633</v>
+        <v>-0.000000000213697384684882</v>
       </c>
       <c r="BM158" s="7">
         <v>0</v>
       </c>
       <c r="BN158" s="7">
-        <v>3023109.57430776</v>
+        <v>3023109.57430779</v>
       </c>
       <c r="BO158" s="7">
         <v>0</v>
@@ -14674,7 +14674,7 @@
         <v>0</v>
       </c>
       <c r="BJ159" s="7">
-        <v>2915788.43397589</v>
+        <v>2915788.43397592</v>
       </c>
       <c r="BK159" s="7">
         <v>0</v>
@@ -14794,7 +14794,7 @@
         <v>0</v>
       </c>
       <c r="BY160" s="7">
-        <v>20456.4061899525</v>
+        <v>20456.406189953</v>
       </c>
       <c r="CB160" s="3" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="BH163" s="7">
-        <v>0.000000000000914962744368463</v>
+        <v>0.0000000000000135419641776167</v>
       </c>
       <c r="BI163" s="7">
         <v>0</v>
@@ -14986,7 +14986,7 @@
         <v>0</v>
       </c>
       <c r="BN163" s="7">
-        <v>4390.22190228729</v>
+        <v>4390.22190228727</v>
       </c>
       <c r="BO163" s="7">
         <v>0</v>
@@ -15070,7 +15070,7 @@
         <v>0</v>
       </c>
       <c r="BQ164" s="7">
-        <v>4368.51223387172</v>
+        <v>4368.51223387163</v>
       </c>
       <c r="BR164" s="7">
         <v>0</v>
@@ -15166,7 +15166,7 @@
         <v>0</v>
       </c>
       <c r="BX165" s="7">
-        <v>4140.47436592439</v>
+        <v>4140.47436592437</v>
       </c>
       <c r="BY165" s="7">
         <v>0</v>
@@ -15211,7 +15211,7 @@
         <v>0</v>
       </c>
       <c r="BN166" s="7">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="BO166" s="7">
         <v>0</v>
@@ -15298,7 +15298,7 @@
         <v>0</v>
       </c>
       <c r="BR167" s="7">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="BS167" s="7">
         <v>0</v>
@@ -15511,7 +15511,7 @@
         <v>0</v>
       </c>
       <c r="BN170" s="7">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="BO170" s="7">
         <v>0</v>
@@ -15604,7 +15604,7 @@
         <v>0</v>
       </c>
       <c r="BT171" s="7">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="BU171" s="7">
         <v>0</v>
@@ -15933,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="E176" s="7">
-        <v>-0.000000000171470466130064</v>
+        <v>-0.000000000000135497978045592</v>
       </c>
       <c r="F176" s="7">
         <v>0</v>
@@ -15969,7 +15969,7 @@
         <v>0</v>
       </c>
       <c r="Q176" s="7">
-        <v>-0.000000000257206209762651</v>
+        <v>-0.000000000000203247370524871</v>
       </c>
       <c r="R176" s="7">
         <v>0</v>
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="F177" s="7">
-        <v>0.000000000000137243937615695</v>
+        <v>0.0000000000000020312876105897</v>
       </c>
       <c r="G177" s="7">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         <v>0</v>
       </c>
       <c r="Y177" s="7">
-        <v>0.000000000000777718806752768</v>
+        <v>0.000000000000011510676567027</v>
       </c>
       <c r="Z177" s="7">
         <v>0</v>
@@ -16328,7 +16328,7 @@
         <v>0</v>
       </c>
       <c r="X178" s="7">
-        <v>60456.4790869308</v>
+        <v>60456.4790869312</v>
       </c>
       <c r="Y178" s="7">
         <v>0</v>
@@ -16388,7 +16388,7 @@
         <v>0</v>
       </c>
       <c r="AR178" s="7">
-        <v>15122.9411248117</v>
+        <v>15122.9411248116</v>
       </c>
       <c r="AS178" s="7">
         <v>0</v>
@@ -16452,7 +16452,7 @@
         <v>0</v>
       </c>
       <c r="I179" s="7">
-        <v>-0.000000000499697217445685</v>
+        <v>-0.000000000000394866615382853</v>
       </c>
       <c r="J179" s="7">
         <v>0</v>
@@ -16494,7 +16494,7 @@
         <v>0</v>
       </c>
       <c r="W179" s="7">
-        <v>5820.73286271002</v>
+        <v>5820.73286271282</v>
       </c>
       <c r="X179" s="7">
         <v>0</v>
@@ -16551,7 +16551,7 @@
         <v>0</v>
       </c>
       <c r="AP179" s="7">
-        <v>3020758.98009959</v>
+        <v>3020758.98009963</v>
       </c>
       <c r="AQ179" s="7">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="G180" s="7">
-        <v>-0.00000000042867661461356</v>
+        <v>-0.000000000000338745300146954</v>
       </c>
       <c r="H180" s="7">
         <v>0</v>
@@ -16657,7 +16657,7 @@
         <v>0</v>
       </c>
       <c r="U180" s="7">
-        <v>-0.000000000183720345295316</v>
+        <v>-0.00000000000014517797656461</v>
       </c>
       <c r="V180" s="7">
         <v>0</v>
@@ -16808,7 +16808,7 @@
         <v>0</v>
       </c>
       <c r="O181" s="7">
-        <v>0.0000000000246838508123097</v>
+        <v>-0.0000000000574814426462061</v>
       </c>
       <c r="P181" s="7">
         <v>0</v>
@@ -16856,7 +16856,7 @@
         <v>0</v>
       </c>
       <c r="AE181" s="7">
-        <v>0.0000000000670827110502536</v>
+        <v>-0.000000000156215942038676</v>
       </c>
       <c r="AF181" s="7">
         <v>0</v>
@@ -16989,7 +16989,7 @@
         <v>0</v>
       </c>
       <c r="S182" s="7">
-        <v>4673.82474422194</v>
+        <v>4673.82474422187</v>
       </c>
       <c r="T182" s="7">
         <v>0</v>
@@ -17064,7 +17064,7 @@
         <v>0</v>
       </c>
       <c r="AR182" s="7">
-        <v>5333.4650651408</v>
+        <v>5333.46506514077</v>
       </c>
       <c r="AS182" s="7">
         <v>0</v>
@@ -17206,7 +17206,7 @@
         <v>0</v>
       </c>
       <c r="AI183" s="7">
-        <v>2069180.95381487</v>
+        <v>2069180.9538149</v>
       </c>
       <c r="AJ183" s="7">
         <v>0</v>
@@ -17351,7 +17351,7 @@
         <v>0</v>
       </c>
       <c r="AA184" s="7">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="AB184" s="7">
         <v>0</v>
@@ -17532,7 +17532,7 @@
         <v>0</v>
       </c>
       <c r="AE185" s="7">
-        <v>-0.0000000000291038304567337</v>
+        <v>0</v>
       </c>
       <c r="AF185" s="7">
         <v>0</v>
@@ -17559,7 +17559,7 @@
         <v>0</v>
       </c>
       <c r="AN185" s="7">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="AO185" s="7">
         <v>0</v>
@@ -17749,7 +17749,7 @@
         <v>0</v>
       </c>
       <c r="AU186" s="7">
-        <v>4368.51223387172</v>
+        <v>4368.51223387163</v>
       </c>
       <c r="AV186" s="7">
         <v>0</v>
@@ -17927,7 +17927,7 @@
         <v>0</v>
       </c>
       <c r="AX187" s="7">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="AY187" s="7">
         <v>0</v>
@@ -18277,7 +18277,7 @@
         <v>0</v>
       </c>
       <c r="BB189" s="7">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="BC189" s="7">
         <v>0</v>
@@ -18392,7 +18392,7 @@
         <v>0</v>
       </c>
       <c r="AJ190" s="7">
-        <v>3605152.2885694</v>
+        <v>3605152.28856941</v>
       </c>
       <c r="AK190" s="7">
         <v>0</v>
@@ -18492,7 +18492,7 @@
         <v>0</v>
       </c>
       <c r="M191" s="7">
-        <v>60946.5548992506</v>
+        <v>60946.5548992509</v>
       </c>
       <c r="N191" s="7">
         <v>0</v>
@@ -18546,7 +18546,7 @@
         <v>0</v>
       </c>
       <c r="AE191" s="7">
-        <v>123739.975098478</v>
+        <v>123739.975098476</v>
       </c>
       <c r="AF191" s="7">
         <v>0</v>
@@ -18655,7 +18655,7 @@
         <v>0</v>
       </c>
       <c r="K192" s="7">
-        <v>273.730001811498</v>
+        <v>273.730001811503</v>
       </c>
       <c r="L192" s="7">
         <v>0</v>
@@ -18691,7 +18691,7 @@
         <v>0</v>
       </c>
       <c r="W192" s="7">
-        <v>0.000000000000113686837721616</v>
+        <v>0</v>
       </c>
       <c r="X192" s="7">
         <v>0</v>
@@ -18736,7 +18736,7 @@
         <v>0</v>
       </c>
       <c r="AL192" s="7">
-        <v>643.118931908688</v>
+        <v>643.118931908693</v>
       </c>
       <c r="AM192" s="7">
         <v>0</v>
@@ -18839,7 +18839,7 @@
         <v>0</v>
       </c>
       <c r="P193" s="7">
-        <v>56830.5846644187</v>
+        <v>56830.5846644188</v>
       </c>
       <c r="Q193" s="7">
         <v>0</v>
@@ -18860,7 +18860,7 @@
         <v>0</v>
       </c>
       <c r="W193" s="7">
-        <v>7550.67554792744</v>
+        <v>7550.67554792739</v>
       </c>
       <c r="X193" s="7">
         <v>0</v>
@@ -18938,7 +18938,7 @@
         <v>0</v>
       </c>
       <c r="AW193" s="7">
-        <v>4140.47436592439</v>
+        <v>4140.47436592437</v>
       </c>
       <c r="AX193" s="7">
         <v>0</v>
@@ -19008,7 +19008,7 @@
         <v>0</v>
       </c>
       <c r="P194" s="7">
-        <v>21889.5244052342</v>
+        <v>21889.5244052343</v>
       </c>
       <c r="Q194" s="7">
         <v>0</v>
@@ -19053,7 +19053,7 @@
         <v>0</v>
       </c>
       <c r="AE194" s="7">
-        <v>-1438.45111196827</v>
+        <v>-1438.45111196792</v>
       </c>
       <c r="AF194" s="7">
         <v>0</v>
@@ -19595,7 +19595,7 @@
         <v>0</v>
       </c>
       <c r="F200" s="2">
-        <v>-0.000000000000137243937615695</v>
+        <v>-0.0000000000000020312876105897</v>
       </c>
       <c r="G200" s="2">
         <v>0</v>
@@ -19773,7 +19773,7 @@
         <v>0</v>
       </c>
       <c r="I201" s="2">
-        <v>-0.000000000112699742463191</v>
+        <v>-0.0000000000000890566613287104</v>
       </c>
       <c r="J201" s="2">
         <v>0</v>
@@ -20123,7 +20123,7 @@
         <v>0</v>
       </c>
       <c r="M203" s="2">
-        <v>40734.7303283633</v>
+        <v>40734.7303283613</v>
       </c>
       <c r="N203" s="2">
         <v>0</v>
@@ -20295,7 +20295,7 @@
         <v>0</v>
       </c>
       <c r="N204" s="2">
-        <v>822.845884522998</v>
+        <v>822.845884522997</v>
       </c>
       <c r="O204" s="2">
         <v>0</v>
@@ -20470,7 +20470,7 @@
         <v>0</v>
       </c>
       <c r="P205" s="2">
-        <v>34699.3669933297</v>
+        <v>34699.3669933295</v>
       </c>
       <c r="Q205" s="2">
         <v>0</v>
@@ -21031,7 +21031,7 @@
         <v>0</v>
       </c>
       <c r="AH208" s="2">
-        <v>2.69177431379901</v>
+        <v>2.691774313799</v>
       </c>
       <c r="AI208" s="2">
         <v>0</v>
@@ -21577,7 +21577,7 @@
         <v>0</v>
       </c>
       <c r="AU211" s="2">
-        <v>21.7096684155722</v>
+        <v>21.7096684156417</v>
       </c>
       <c r="AV211" s="2">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="C212" s="2">
-        <v>42469.4304457101</v>
+        <v>42469.4304457103</v>
       </c>
       <c r="D212" s="2">
         <v>0</v>
@@ -21804,7 +21804,7 @@
         <v>0</v>
       </c>
       <c r="J213" s="2">
-        <v>62501.1156779948</v>
+        <v>62501.1156779955</v>
       </c>
       <c r="K213" s="2">
         <v>0</v>
@@ -21979,7 +21979,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="2">
-        <v>273.730001811498</v>
+        <v>273.730001811503</v>
       </c>
       <c r="M214" s="2">
         <v>0</v>
@@ -22196,7 +22196,7 @@
         <v>0</v>
       </c>
       <c r="AB215" s="2">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="AC215" s="2">
         <v>0</v>
@@ -22398,7 +22398,7 @@
         <v>0</v>
       </c>
       <c r="AM216" s="2">
-        <v>643.118931908688</v>
+        <v>643.118931908693</v>
       </c>
       <c r="AN216" s="2">
         <v>0</v>
@@ -22561,7 +22561,7 @@
         <v>0</v>
       </c>
       <c r="AK217" s="2">
-        <v>3605152.2885694</v>
+        <v>3605152.28856941</v>
       </c>
       <c r="AL217" s="2">
         <v>0</v>
@@ -22742,7 +22742,7 @@
         <v>0</v>
       </c>
       <c r="AO218" s="2">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="AP218" s="2">
         <v>0</v>
@@ -22917,7 +22917,7 @@
         <v>0</v>
       </c>
       <c r="AQ219" s="2">
-        <v>2915788.43397589</v>
+        <v>2915788.43397592</v>
       </c>
       <c r="AR219" s="2">
         <v>0</v>
@@ -23101,7 +23101,7 @@
         <v>0</v>
       </c>
       <c r="AV220" s="2">
-        <v>4368.51223387172</v>
+        <v>4368.51223387163</v>
       </c>
       <c r="AW220" s="2">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>0</v>
       </c>
       <c r="AY221" s="2">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="AZ221" s="2">
         <v>0</v>
@@ -23629,7 +23629,7 @@
         <v>0</v>
       </c>
       <c r="BC223" s="2">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
     </row>
     <row r="224">
@@ -23654,7 +23654,7 @@
         <v>0</v>
       </c>
       <c r="G224" s="2">
-        <v>-0.0000000000000000612791551925605</v>
+        <v>-0.0000000000000000000484235088085785</v>
       </c>
       <c r="H224" s="2">
         <v>0</v>
@@ -23675,7 +23675,7 @@
         <v>0</v>
       </c>
       <c r="N224" s="2">
-        <v>597.728616315919</v>
+        <v>597.72861631592</v>
       </c>
       <c r="O224" s="2">
         <v>0</v>
@@ -23759,7 +23759,7 @@
         <v>0</v>
       </c>
       <c r="AP224" s="2">
-        <v>77930.0144199092</v>
+        <v>77930.014419904</v>
       </c>
       <c r="AQ224" s="2">
         <v>0</v>

--- a/data/ecc_supply_to_mcc_with_losses.xlsx
+++ b/data/ecc_supply_to_mcc_with_losses.xlsx
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="BJ13" s="8">
-        <v>5820.73286270896</v>
+        <v>5820.73215535619</v>
       </c>
       <c r="BK13" s="8">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="BN13" s="8">
-        <v>67354.0211167639</v>
+        <v>67354.02046594</v>
       </c>
       <c r="BO13" s="8">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="BX13" s="8">
-        <v>3155.64534081533</v>
+        <v>3155.63573488976</v>
       </c>
       <c r="BY13" s="8">
         <v>0</v>
@@ -6008,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="8">
-        <v>54768.7189038251</v>
+        <v>54768.4671959323</v>
       </c>
       <c r="BJ42" s="8">
         <v>0</v>
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="BX49" s="8">
-        <v>4140.47436592437</v>
+        <v>4140.46176213519</v>
       </c>
       <c r="BY49" s="8">
         <v>0</v>
@@ -8093,7 +8093,7 @@
         <v>0</v>
       </c>
       <c r="BJ61" s="8">
-        <v>42469.4304457103</v>
+        <v>42469.4252846988</v>
       </c>
       <c r="BK61" s="8">
         <v>0</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="BJ68" s="8">
-        <v>62501.1156779955</v>
+        <v>62501.108082674</v>
       </c>
       <c r="BK68" s="8">
         <v>0</v>
@@ -8647,7 +8647,7 @@
         <v>0</v>
       </c>
       <c r="BX69" s="8">
-        <v>86639.6929976091</v>
+        <v>86639.4292625082</v>
       </c>
       <c r="BY69" s="8">
         <v>0</v>
@@ -8708,7 +8708,7 @@
         <v>0</v>
       </c>
       <c r="BW70" s="8">
-        <v>273.730001811503</v>
+        <v>273.729168565133</v>
       </c>
       <c r="BX70" s="8">
         <v>0</v>
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="BN74" s="8">
-        <v>2369.24361812096</v>
+        <v>2369.24359522759</v>
       </c>
       <c r="BO74" s="8">
         <v>0</v>
@@ -9641,7 +9641,7 @@
         <v>0</v>
       </c>
       <c r="BN85" s="8">
-        <v>4830.44426252755</v>
+        <v>4830.44421585225</v>
       </c>
       <c r="BO85" s="8">
         <v>0</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="BO86" s="8">
-        <v>4830.44426252755</v>
+        <v>4830.44421585225</v>
       </c>
       <c r="BP86" s="8">
         <v>0</v>
@@ -10214,7 +10214,7 @@
         <v>0</v>
       </c>
       <c r="BM94" s="8">
-        <v>10007.2898093626</v>
+        <v>10007.2438175286</v>
       </c>
       <c r="BN94" s="8">
         <v>0</v>
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="BU95" s="8">
-        <v>3605152.28856941</v>
+        <v>3605152.27697659</v>
       </c>
       <c r="BV95" s="8">
         <v>0</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="BX96" s="8">
-        <v>643.118931908693</v>
+        <v>643.116974225897</v>
       </c>
       <c r="BY96" s="8">
         <v>0</v>
@@ -10436,7 +10436,7 @@
         <v>0</v>
       </c>
       <c r="BW97" s="8">
-        <v>643.118931908693</v>
+        <v>643.116974225897</v>
       </c>
       <c r="BX97" s="8">
         <v>0</v>
@@ -10497,7 +10497,7 @@
         <v>0</v>
       </c>
       <c r="BV98" s="8">
-        <v>184686.529997727</v>
+        <v>184686.52821315</v>
       </c>
       <c r="BW98" s="8">
         <v>0</v>
@@ -10543,7 +10543,7 @@
         <v>0</v>
       </c>
       <c r="BP99" s="8">
-        <v>184686.529997727</v>
+        <v>184686.52821315</v>
       </c>
       <c r="BQ99" s="8">
         <v>0</v>
@@ -10586,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="8">
-        <v>20810.7013079177</v>
+        <v>20810.6056654072</v>
       </c>
       <c r="BJ100" s="8">
         <v>0</v>
@@ -10595,13 +10595,13 @@
         <v>0</v>
       </c>
       <c r="BL100" s="8">
-        <v>-0.000000000213697384684882</v>
+        <v>-0.000000000213697311244698</v>
       </c>
       <c r="BM100" s="8">
         <v>0</v>
       </c>
       <c r="BN100" s="8">
-        <v>3023109.57430779</v>
+        <v>3023109.54509628</v>
       </c>
       <c r="BO100" s="8">
         <v>0</v>
@@ -10653,7 +10653,7 @@
         <v>0</v>
       </c>
       <c r="BJ101" s="8">
-        <v>2915788.43397592</v>
+        <v>2915788.07964064</v>
       </c>
       <c r="BK101" s="8">
         <v>0</v>
@@ -10762,7 +10762,7 @@
         <v>0</v>
       </c>
       <c r="BY102" s="8">
-        <v>20456.406189953</v>
+        <v>20456.3121757237</v>
       </c>
     </row>
     <row r="103">
@@ -10903,7 +10903,7 @@
         <v>0</v>
       </c>
       <c r="BH105" s="8">
-        <v>0.0000000000000135419641776167</v>
+        <v>0.0000000000000135420233746064</v>
       </c>
       <c r="BI105" s="8">
         <v>0</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="BN105" s="8">
-        <v>4390.22190228727</v>
+        <v>4390.22185986572</v>
       </c>
       <c r="BO105" s="8">
         <v>0</v>
@@ -10994,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="BQ106" s="8">
-        <v>4368.51223387163</v>
+        <v>4368.51219165986</v>
       </c>
       <c r="BR106" s="8">
         <v>0</v>
@@ -11113,7 +11113,7 @@
         <v>0</v>
       </c>
       <c r="BN108" s="8">
-        <v>82.0916287907193</v>
+        <v>82.0916279974897</v>
       </c>
       <c r="BO108" s="8">
         <v>0</v>
@@ -11189,7 +11189,7 @@
         <v>0</v>
       </c>
       <c r="BR109" s="8">
-        <v>82.0916287907193</v>
+        <v>82.0916279974897</v>
       </c>
       <c r="BS109" s="8">
         <v>0</v>
@@ -11369,7 +11369,7 @@
         <v>0</v>
       </c>
       <c r="BN112" s="8">
-        <v>43.2061204161677</v>
+        <v>43.2061199986785</v>
       </c>
       <c r="BO112" s="8">
         <v>0</v>
@@ -11451,7 +11451,7 @@
         <v>0</v>
       </c>
       <c r="BT113" s="8">
-        <v>43.2061204161677</v>
+        <v>43.2061199986785</v>
       </c>
       <c r="BU113" s="8">
         <v>0</v>
@@ -11674,7 +11674,7 @@
         <v>0</v>
       </c>
       <c r="BJ119" s="7">
-        <v>42469.4304457103</v>
+        <v>42469.4252846988</v>
       </c>
       <c r="BK119" s="7">
         <v>0</v>
@@ -12199,7 +12199,7 @@
         <v>0</v>
       </c>
       <c r="BJ126" s="7">
-        <v>62501.1156779955</v>
+        <v>62501.108082674</v>
       </c>
       <c r="BK126" s="7">
         <v>0</v>
@@ -12316,7 +12316,7 @@
         <v>0</v>
       </c>
       <c r="BX127" s="7">
-        <v>86639.6929976091</v>
+        <v>86639.4292625082</v>
       </c>
       <c r="BY127" s="7">
         <v>0</v>
@@ -12388,7 +12388,7 @@
         <v>0</v>
       </c>
       <c r="BW128" s="7">
-        <v>273.730001811503</v>
+        <v>273.729168565133</v>
       </c>
       <c r="BX128" s="7">
         <v>0</v>
@@ -12424,7 +12424,7 @@
         <v>0</v>
       </c>
       <c r="BJ129" s="7">
-        <v>5820.73286270896</v>
+        <v>5820.73215535619</v>
       </c>
       <c r="BK129" s="7">
         <v>0</v>
@@ -12436,7 +12436,7 @@
         <v>0</v>
       </c>
       <c r="BN129" s="7">
-        <v>67354.0211167639</v>
+        <v>67354.02046594</v>
       </c>
       <c r="BO129" s="7">
         <v>0</v>
@@ -12466,7 +12466,7 @@
         <v>0</v>
       </c>
       <c r="BX129" s="7">
-        <v>3155.64534081533</v>
+        <v>3155.63573488976</v>
       </c>
       <c r="BY129" s="7">
         <v>0</v>
@@ -12661,7 +12661,7 @@
         <v>0</v>
       </c>
       <c r="BN132" s="7">
-        <v>2369.24361812096</v>
+        <v>2369.24359522759</v>
       </c>
       <c r="BO132" s="7">
         <v>0</v>
@@ -12930,7 +12930,7 @@
         <v>0</v>
       </c>
       <c r="CD135" s="2">
-        <v>4673.82474422187</v>
+        <v>4673.80326410328</v>
       </c>
     </row>
     <row r="136">
@@ -13230,7 +13230,7 @@
         <v>0</v>
       </c>
       <c r="CD139" s="2">
-        <v>13371.4084106407</v>
+        <v>13371.3847186926</v>
       </c>
     </row>
     <row r="140">
@@ -13305,7 +13305,7 @@
         <v>0</v>
       </c>
       <c r="CD140" s="2">
-        <v>60456.4790869312</v>
+        <v>60456.2012390418</v>
       </c>
     </row>
     <row r="141">
@@ -13380,7 +13380,7 @@
         <v>0</v>
       </c>
       <c r="CD141" s="2">
-        <v>0.000000000000011510676567027</v>
+        <v>0.000000000000011510726884499</v>
       </c>
     </row>
     <row r="142">
@@ -13486,7 +13486,7 @@
         <v>0</v>
       </c>
       <c r="BN143" s="7">
-        <v>4830.44426252755</v>
+        <v>4830.44421585225</v>
       </c>
       <c r="BO143" s="7">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>0</v>
       </c>
       <c r="BO144" s="7">
-        <v>4830.44426252755</v>
+        <v>4830.44421585225</v>
       </c>
       <c r="BP144" s="7">
         <v>0</v>
@@ -13830,7 +13830,7 @@
         <v>0</v>
       </c>
       <c r="CD147" s="2">
-        <v>122301.523986508</v>
+        <v>122301.529401723</v>
       </c>
     </row>
     <row r="148">
@@ -14052,7 +14052,7 @@
         </is>
       </c>
       <c r="CC150" s="2">
-        <v>23.1502244399504</v>
+        <v>22.7134277524042</v>
       </c>
       <c r="CD150" s="2">
         <v>0</v>
@@ -14130,7 +14130,7 @@
         <v>0</v>
       </c>
       <c r="CD151" s="2">
-        <v>2069180.9538149</v>
+        <v>2069180.93382096</v>
       </c>
     </row>
     <row r="152">
@@ -14158,7 +14158,7 @@
         <v>0</v>
       </c>
       <c r="BM152" s="7">
-        <v>10007.2898093626</v>
+        <v>10007.2438175286</v>
       </c>
       <c r="BN152" s="7">
         <v>0</v>
@@ -14257,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="BU153" s="7">
-        <v>3605152.28856941</v>
+        <v>3605152.27697659</v>
       </c>
       <c r="BV153" s="7">
         <v>0</v>
@@ -14341,7 +14341,7 @@
         <v>0</v>
       </c>
       <c r="BX154" s="7">
-        <v>643.118931908693</v>
+        <v>643.116974225897</v>
       </c>
       <c r="BY154" s="7">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="BW155" s="7">
-        <v>643.118931908693</v>
+        <v>643.116974225897</v>
       </c>
       <c r="BX155" s="7">
         <v>0</v>
@@ -14485,7 +14485,7 @@
         <v>0</v>
       </c>
       <c r="BV156" s="7">
-        <v>184686.529997727</v>
+        <v>184686.52821315</v>
       </c>
       <c r="BW156" s="7">
         <v>0</v>
@@ -14542,7 +14542,7 @@
         <v>0</v>
       </c>
       <c r="BP157" s="7">
-        <v>184686.529997727</v>
+        <v>184686.52821315</v>
       </c>
       <c r="BQ157" s="7">
         <v>0</v>
@@ -14596,7 +14596,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="7">
-        <v>75579.4202117428</v>
+        <v>75579.0728613395</v>
       </c>
       <c r="BJ158" s="7">
         <v>0</v>
@@ -14605,13 +14605,13 @@
         <v>0</v>
       </c>
       <c r="BL158" s="7">
-        <v>-0.000000000213697384684882</v>
+        <v>-0.000000000213697311244698</v>
       </c>
       <c r="BM158" s="7">
         <v>0</v>
       </c>
       <c r="BN158" s="7">
-        <v>3023109.57430779</v>
+        <v>3023109.54509628</v>
       </c>
       <c r="BO158" s="7">
         <v>0</v>
@@ -14674,7 +14674,7 @@
         <v>0</v>
       </c>
       <c r="BJ159" s="7">
-        <v>2915788.43397592</v>
+        <v>2915788.07964064</v>
       </c>
       <c r="BK159" s="7">
         <v>0</v>
@@ -14794,7 +14794,7 @@
         <v>0</v>
       </c>
       <c r="BY160" s="7">
-        <v>20456.406189953</v>
+        <v>20456.3121757237</v>
       </c>
       <c r="CB160" s="3" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="BH163" s="7">
-        <v>0.0000000000000135419641776167</v>
+        <v>0.0000000000000135420233746064</v>
       </c>
       <c r="BI163" s="7">
         <v>0</v>
@@ -14986,7 +14986,7 @@
         <v>0</v>
       </c>
       <c r="BN163" s="7">
-        <v>4390.22190228727</v>
+        <v>4390.22185986572</v>
       </c>
       <c r="BO163" s="7">
         <v>0</v>
@@ -15070,7 +15070,7 @@
         <v>0</v>
       </c>
       <c r="BQ164" s="7">
-        <v>4368.51223387163</v>
+        <v>4368.51219165986</v>
       </c>
       <c r="BR164" s="7">
         <v>0</v>
@@ -15166,7 +15166,7 @@
         <v>0</v>
       </c>
       <c r="BX165" s="7">
-        <v>4140.47436592437</v>
+        <v>4140.46176213519</v>
       </c>
       <c r="BY165" s="7">
         <v>0</v>
@@ -15211,7 +15211,7 @@
         <v>0</v>
       </c>
       <c r="BN166" s="7">
-        <v>82.0916287907193</v>
+        <v>82.0916279974897</v>
       </c>
       <c r="BO166" s="7">
         <v>0</v>
@@ -15298,7 +15298,7 @@
         <v>0</v>
       </c>
       <c r="BR167" s="7">
-        <v>82.0916287907193</v>
+        <v>82.0916279974897</v>
       </c>
       <c r="BS167" s="7">
         <v>0</v>
@@ -15511,7 +15511,7 @@
         <v>0</v>
       </c>
       <c r="BN170" s="7">
-        <v>43.2061204161677</v>
+        <v>43.2061199986785</v>
       </c>
       <c r="BO170" s="7">
         <v>0</v>
@@ -15604,7 +15604,7 @@
         <v>0</v>
       </c>
       <c r="BT171" s="7">
-        <v>43.2061204161677</v>
+        <v>43.2061199986785</v>
       </c>
       <c r="BU171" s="7">
         <v>0</v>
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="F177" s="7">
-        <v>0.0000000000000020312876105897</v>
+        <v>0.00000000000000203129649010748</v>
       </c>
       <c r="G177" s="7">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         <v>0</v>
       </c>
       <c r="Y177" s="7">
-        <v>0.000000000000011510676567027</v>
+        <v>0.000000000000011510726884499</v>
       </c>
       <c r="Z177" s="7">
         <v>0</v>
@@ -16328,7 +16328,7 @@
         <v>0</v>
       </c>
       <c r="X178" s="7">
-        <v>60456.4790869312</v>
+        <v>60456.2012390418</v>
       </c>
       <c r="Y178" s="7">
         <v>0</v>
@@ -16388,7 +16388,7 @@
         <v>0</v>
       </c>
       <c r="AR178" s="7">
-        <v>15122.9411248116</v>
+        <v>15122.8716222978</v>
       </c>
       <c r="AS178" s="7">
         <v>0</v>
@@ -16494,7 +16494,7 @@
         <v>0</v>
       </c>
       <c r="W179" s="7">
-        <v>5820.73286271282</v>
+        <v>5820.73215535935</v>
       </c>
       <c r="X179" s="7">
         <v>0</v>
@@ -16551,7 +16551,7 @@
         <v>0</v>
       </c>
       <c r="AP179" s="7">
-        <v>3020758.98009963</v>
+        <v>3020758.61300801</v>
       </c>
       <c r="AQ179" s="7">
         <v>0</v>
@@ -16808,7 +16808,7 @@
         <v>0</v>
       </c>
       <c r="O181" s="7">
-        <v>-0.0000000000574814426462061</v>
+        <v>-0.0000000000574814228918805</v>
       </c>
       <c r="P181" s="7">
         <v>0</v>
@@ -16856,7 +16856,7 @@
         <v>0</v>
       </c>
       <c r="AE181" s="7">
-        <v>-0.000000000156215942038676</v>
+        <v>-0.000000000156215888352818</v>
       </c>
       <c r="AF181" s="7">
         <v>0</v>
@@ -16989,7 +16989,7 @@
         <v>0</v>
       </c>
       <c r="S182" s="7">
-        <v>4673.82474422187</v>
+        <v>4673.80326410328</v>
       </c>
       <c r="T182" s="7">
         <v>0</v>
@@ -17064,7 +17064,7 @@
         <v>0</v>
       </c>
       <c r="AR182" s="7">
-        <v>5333.46506514077</v>
+        <v>5333.44055342533</v>
       </c>
       <c r="AS182" s="7">
         <v>0</v>
@@ -17140,7 +17140,7 @@
         <v>0</v>
       </c>
       <c r="M183" s="7">
-        <v>1032997.84914179</v>
+        <v>1032997.83916021</v>
       </c>
       <c r="N183" s="7">
         <v>0</v>
@@ -17206,7 +17206,7 @@
         <v>0</v>
       </c>
       <c r="AI183" s="7">
-        <v>2069180.9538149</v>
+        <v>2069180.93382096</v>
       </c>
       <c r="AJ183" s="7">
         <v>0</v>
@@ -17351,7 +17351,7 @@
         <v>0</v>
       </c>
       <c r="AA184" s="7">
-        <v>4830.44426252755</v>
+        <v>4830.44421585225</v>
       </c>
       <c r="AB184" s="7">
         <v>0</v>
@@ -17559,7 +17559,7 @@
         <v>0</v>
       </c>
       <c r="AN185" s="7">
-        <v>184686.529997727</v>
+        <v>184686.52821315</v>
       </c>
       <c r="AO185" s="7">
         <v>0</v>
@@ -17749,7 +17749,7 @@
         <v>0</v>
       </c>
       <c r="AU186" s="7">
-        <v>4368.51223387163</v>
+        <v>4368.51219165986</v>
       </c>
       <c r="AV186" s="7">
         <v>0</v>
@@ -17927,7 +17927,7 @@
         <v>0</v>
       </c>
       <c r="AX187" s="7">
-        <v>82.0916287907193</v>
+        <v>82.0916279974897</v>
       </c>
       <c r="AY187" s="7">
         <v>0</v>
@@ -18277,7 +18277,7 @@
         <v>0</v>
       </c>
       <c r="BB189" s="7">
-        <v>43.2061204161677</v>
+        <v>43.2061199986785</v>
       </c>
       <c r="BC189" s="7">
         <v>0</v>
@@ -18353,7 +18353,7 @@
         <v>0</v>
       </c>
       <c r="W190" s="7">
-        <v>0.000000000465661287307739</v>
+        <v>0</v>
       </c>
       <c r="X190" s="7">
         <v>0</v>
@@ -18392,7 +18392,7 @@
         <v>0</v>
       </c>
       <c r="AJ190" s="7">
-        <v>3605152.28856941</v>
+        <v>3605152.27697659</v>
       </c>
       <c r="AK190" s="7">
         <v>0</v>
@@ -18492,7 +18492,7 @@
         <v>0</v>
       </c>
       <c r="M191" s="7">
-        <v>60946.5548992509</v>
+        <v>60946.5543103406</v>
       </c>
       <c r="N191" s="7">
         <v>0</v>
@@ -18546,7 +18546,7 @@
         <v>0</v>
       </c>
       <c r="AE191" s="7">
-        <v>123739.975098476</v>
+        <v>123739.97390281</v>
       </c>
       <c r="AF191" s="7">
         <v>0</v>
@@ -18655,7 +18655,7 @@
         <v>0</v>
       </c>
       <c r="K192" s="7">
-        <v>273.730001811503</v>
+        <v>273.729168565133</v>
       </c>
       <c r="L192" s="7">
         <v>0</v>
@@ -18691,7 +18691,7 @@
         <v>0</v>
       </c>
       <c r="W192" s="7">
-        <v>0</v>
+        <v>0.000000000000113686837721616</v>
       </c>
       <c r="X192" s="7">
         <v>0</v>
@@ -18736,7 +18736,7 @@
         <v>0</v>
       </c>
       <c r="AL192" s="7">
-        <v>643.118931908693</v>
+        <v>643.116974225897</v>
       </c>
       <c r="AM192" s="7">
         <v>0</v>
@@ -18839,7 +18839,7 @@
         <v>0</v>
       </c>
       <c r="P193" s="7">
-        <v>56830.5846644188</v>
+        <v>56830.5846529477</v>
       </c>
       <c r="Q193" s="7">
         <v>0</v>
@@ -18860,7 +18860,7 @@
         <v>0</v>
       </c>
       <c r="W193" s="7">
-        <v>7550.67554792739</v>
+        <v>7550.65256333328</v>
       </c>
       <c r="X193" s="7">
         <v>0</v>
@@ -18893,7 +18893,7 @@
         <v>0</v>
       </c>
       <c r="AH193" s="7">
-        <v>13.3720401395176</v>
+        <v>13.1197374953758</v>
       </c>
       <c r="AI193" s="7">
         <v>0</v>
@@ -18938,7 +18938,7 @@
         <v>0</v>
       </c>
       <c r="AW193" s="7">
-        <v>4140.47436592437</v>
+        <v>4140.46176213519</v>
       </c>
       <c r="AX193" s="7">
         <v>0</v>
@@ -19008,7 +19008,7 @@
         <v>0</v>
       </c>
       <c r="P194" s="7">
-        <v>21889.5244052343</v>
+        <v>21889.524400816</v>
       </c>
       <c r="Q194" s="7">
         <v>0</v>
@@ -19053,7 +19053,7 @@
         <v>0</v>
       </c>
       <c r="AE194" s="7">
-        <v>-1438.45111196792</v>
+        <v>-1438.44450108664</v>
       </c>
       <c r="AF194" s="7">
         <v>0</v>
@@ -19062,7 +19062,7 @@
         <v>0</v>
       </c>
       <c r="AH194" s="7">
-        <v>5.33289668659379</v>
+        <v>5.23227599439391</v>
       </c>
       <c r="AI194" s="7">
         <v>0</v>
@@ -19595,7 +19595,7 @@
         <v>0</v>
       </c>
       <c r="F200" s="2">
-        <v>-0.0000000000000020312876105897</v>
+        <v>-0.00000000000000203129649010748</v>
       </c>
       <c r="G200" s="2">
         <v>0</v>
@@ -19948,7 +19948,7 @@
         <v>0</v>
       </c>
       <c r="K202" s="2">
-        <v>77382.6420272566</v>
+        <v>77382.4064710329</v>
       </c>
       <c r="L202" s="2">
         <v>0</v>
@@ -20123,7 +20123,7 @@
         <v>0</v>
       </c>
       <c r="M203" s="2">
-        <v>40734.7303283613</v>
+        <v>40734.7299347524</v>
       </c>
       <c r="N203" s="2">
         <v>0</v>
@@ -20470,7 +20470,7 @@
         <v>0</v>
       </c>
       <c r="P205" s="2">
-        <v>34699.3669933295</v>
+        <v>34699.3669863255</v>
       </c>
       <c r="Q205" s="2">
         <v>0</v>
@@ -21031,7 +21031,7 @@
         <v>0</v>
       </c>
       <c r="AH208" s="2">
-        <v>2.691774313799</v>
+        <v>2.64098611919903</v>
       </c>
       <c r="AI208" s="2">
         <v>0</v>
@@ -21206,7 +21206,7 @@
         <v>0</v>
       </c>
       <c r="AJ209" s="2">
-        <v>10697451.7977645</v>
+        <v>10697451.7633655</v>
       </c>
       <c r="AK209" s="2">
         <v>0</v>
@@ -21577,7 +21577,7 @@
         <v>0</v>
       </c>
       <c r="AU211" s="2">
-        <v>21.7096684156417</v>
+        <v>21.7096682058663</v>
       </c>
       <c r="AV211" s="2">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="C212" s="2">
-        <v>42469.4304457103</v>
+        <v>42469.4252846988</v>
       </c>
       <c r="D212" s="2">
         <v>0</v>
@@ -21804,7 +21804,7 @@
         <v>0</v>
       </c>
       <c r="J213" s="2">
-        <v>62501.1156779955</v>
+        <v>62501.108082674</v>
       </c>
       <c r="K213" s="2">
         <v>0</v>
@@ -21979,7 +21979,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="2">
-        <v>273.730001811503</v>
+        <v>273.729168565133</v>
       </c>
       <c r="M214" s="2">
         <v>0</v>
@@ -22196,7 +22196,7 @@
         <v>0</v>
       </c>
       <c r="AB215" s="2">
-        <v>4830.44426252755</v>
+        <v>4830.44421585225</v>
       </c>
       <c r="AC215" s="2">
         <v>0</v>
@@ -22398,7 +22398,7 @@
         <v>0</v>
       </c>
       <c r="AM216" s="2">
-        <v>643.118931908693</v>
+        <v>643.116974225897</v>
       </c>
       <c r="AN216" s="2">
         <v>0</v>
@@ -22561,7 +22561,7 @@
         <v>0</v>
       </c>
       <c r="AK217" s="2">
-        <v>3605152.28856941</v>
+        <v>3605152.27697659</v>
       </c>
       <c r="AL217" s="2">
         <v>0</v>
@@ -22742,7 +22742,7 @@
         <v>0</v>
       </c>
       <c r="AO218" s="2">
-        <v>184686.529997727</v>
+        <v>184686.52821315</v>
       </c>
       <c r="AP218" s="2">
         <v>0</v>
@@ -22917,7 +22917,7 @@
         <v>0</v>
       </c>
       <c r="AQ219" s="2">
-        <v>2915788.43397592</v>
+        <v>2915788.07964064</v>
       </c>
       <c r="AR219" s="2">
         <v>0</v>
@@ -23101,7 +23101,7 @@
         <v>0</v>
       </c>
       <c r="AV220" s="2">
-        <v>4368.51223387163</v>
+        <v>4368.51219165986</v>
       </c>
       <c r="AW220" s="2">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>0</v>
       </c>
       <c r="AY221" s="2">
-        <v>82.0916287907193</v>
+        <v>82.0916279974897</v>
       </c>
       <c r="AZ221" s="2">
         <v>0</v>
@@ -23629,7 +23629,7 @@
         <v>0</v>
       </c>
       <c r="BC223" s="2">
-        <v>43.2061204161677</v>
+        <v>43.2061199986785</v>
       </c>
     </row>
     <row r="224">
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="K224" s="2">
-        <v>8386.09187367954</v>
+        <v>8386.06634604076</v>
       </c>
       <c r="L224" s="2">
         <v>0</v>
@@ -23735,7 +23735,7 @@
         <v>0</v>
       </c>
       <c r="AH224" s="2">
-        <v>1.75351330004002</v>
+        <v>1.72042814343549</v>
       </c>
       <c r="AI224" s="2">
         <v>0</v>
@@ -23759,7 +23759,7 @@
         <v>0</v>
       </c>
       <c r="AP224" s="2">
-        <v>77930.014419904</v>
+        <v>77930.0049496157</v>
       </c>
       <c r="AQ224" s="2">
         <v>0</v>
@@ -23835,7 +23835,7 @@
         <v>0</v>
       </c>
       <c r="K225" s="2">
-        <v>597.229094861451</v>
+        <v>597.227276869372</v>
       </c>
       <c r="L225" s="2">
         <v>0</v>
